--- a/data/raw/Kawak/2023.xlsx
+++ b/data/raw/Kawak/2023.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/Kawak/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Sistema_Indicadores_Poli/data/raw/Kawak/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{316A0730-C110-4A0A-8242-46CB03B5E10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{316A0730-C110-4A0A-8242-46CB03B5E10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB9CFA3C-F7AF-40B2-9A75-71CE6291FAFB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26489857-277B-4D47-8B6B-F0B2F36B12DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$V$290</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1157,7 +1160,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1171,6 +1174,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1269,7 +1273,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{2ADA098F-B079-4EF8-8FCD-650117B7FCA0}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
